--- a/reports/Web/selenium-report.xlsx
+++ b/reports/Web/selenium-report.xlsx
@@ -45,7 +45,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>52.57 seconds</t>
+    <t>49.37 seconds</t>
   </si>
   <si>
     <t>Browser</t>
@@ -63,7 +63,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>8/27/2026, 4:40:42 PM</t>
+    <t>10/8/2026, 3:16:04 PM</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -102,7 +102,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>2026-08-27T16:39:53.894Z</t>
+    <t>2026-10-08T15:15:24.554Z</t>
   </si>
   <si>
     <t>WEB-002</t>
@@ -111,7 +111,7 @@
     <t>Registration Screen &amp; Student Account Form</t>
   </si>
   <si>
-    <t>2026-08-27T16:39:54.050Z</t>
+    <t>2026-10-08T15:15:24.677Z</t>
   </si>
   <si>
     <t>WEB-003</t>
@@ -120,7 +120,7 @@
     <t>Login Screen &amp; Credentials Form Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T16:39:54.197Z</t>
+    <t>2026-10-08T15:15:24.774Z</t>
   </si>
   <si>
     <t>WEB-004</t>
@@ -129,7 +129,7 @@
     <t>Invalid Login Error Notice &amp; Alert Verification</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:15.443Z</t>
+    <t>2026-10-08T15:15:46.013Z</t>
   </si>
   <si>
     <t>WEB-005</t>
@@ -138,7 +138,7 @@
     <t>Password Reset Interface &amp; Recovery Options</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:15.642Z</t>
+    <t>2026-10-08T15:15:46.131Z</t>
   </si>
   <si>
     <t>WEB-006</t>
@@ -150,7 +150,7 @@
     <t>Dashboard</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:15.791Z</t>
+    <t>2026-10-08T15:15:46.206Z</t>
   </si>
   <si>
     <t>WEB-007</t>
@@ -159,7 +159,7 @@
     <t>Dashboard Progress Widgets &amp; XP Display</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:15.916Z</t>
+    <t>2026-10-08T15:15:46.302Z</t>
   </si>
   <si>
     <t>WEB-008</t>
@@ -171,7 +171,7 @@
     <t>Grade Selection</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:16.198Z</t>
+    <t>2026-10-08T15:15:46.482Z</t>
   </si>
   <si>
     <t>WEB-009</t>
@@ -180,7 +180,7 @@
     <t>Switch Grade — Class 7 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:16.483Z</t>
+    <t>2026-10-08T15:15:46.663Z</t>
   </si>
   <si>
     <t>WEB-010</t>
@@ -189,7 +189,7 @@
     <t>Switch Grade — Class 8 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:16.767Z</t>
+    <t>2026-10-08T15:15:46.836Z</t>
   </si>
   <si>
     <t>WEB-011</t>
@@ -198,7 +198,7 @@
     <t>Switch Grade — Class 9 CBSE/ICSE Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:17.048Z</t>
+    <t>2026-10-08T15:15:46.985Z</t>
   </si>
   <si>
     <t>WEB-012</t>
@@ -207,7 +207,7 @@
     <t>Switch Grade — Class 10 Board Exam Curriculum</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:17.353Z</t>
+    <t>2026-10-08T15:15:47.146Z</t>
   </si>
   <si>
     <t>WEB-013</t>
@@ -219,7 +219,7 @@
     <t>Subject Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:18.406Z</t>
+    <t>2026-10-08T15:15:48.114Z</t>
   </si>
   <si>
     <t>WEB-014</t>
@@ -228,7 +228,7 @@
     <t>Explore Physics Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:19.295Z</t>
+    <t>2026-10-08T15:15:49.097Z</t>
   </si>
   <si>
     <t>WEB-015</t>
@@ -237,7 +237,7 @@
     <t>Explore Chemistry Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:20.148Z</t>
+    <t>2026-10-08T15:15:49.405Z</t>
   </si>
   <si>
     <t>WEB-016</t>
@@ -246,7 +246,7 @@
     <t>Explore Biology Subject Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:21.023Z</t>
+    <t>2026-10-08T15:15:49.768Z</t>
   </si>
   <si>
     <t>WEB-017</t>
@@ -255,7 +255,7 @@
     <t>Explore History &amp; Civics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:22.114Z</t>
+    <t>2026-10-08T15:15:50.186Z</t>
   </si>
   <si>
     <t>WEB-018</t>
@@ -264,7 +264,7 @@
     <t>Explore Geography &amp; Economics Stream Grid</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:22.792Z</t>
+    <t>2026-10-08T15:15:50.559Z</t>
   </si>
   <si>
     <t>WEB-019</t>
@@ -276,7 +276,7 @@
     <t>Chapter Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:23.115Z</t>
+    <t>2026-10-08T15:15:50.712Z</t>
   </si>
   <si>
     <t>WEB-020</t>
@@ -288,7 +288,7 @@
     <t>Lesson Navigation</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:24.600Z</t>
+    <t>2026-10-08T15:15:51.933Z</t>
   </si>
   <si>
     <t>WEB-021</t>
@@ -300,7 +300,7 @@
     <t>Lesson Rendering</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:24.874Z</t>
+    <t>2026-10-08T15:15:52.135Z</t>
   </si>
   <si>
     <t>WEB-022</t>
@@ -309,7 +309,7 @@
     <t>Verify All 13 Pedagogical Layout Sections</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:25.217Z</t>
+    <t>2026-10-08T15:15:52.332Z</t>
   </si>
   <si>
     <t>WEB-023</t>
@@ -321,7 +321,7 @@
     <t>Lesson Progress</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:25.720Z</t>
+    <t>2026-10-08T15:15:52.578Z</t>
   </si>
   <si>
     <t>WEB-024</t>
@@ -330,7 +330,7 @@
     <t>XP Gamification Increment (+100 XP)</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:26.121Z</t>
+    <t>2026-10-08T15:15:52.804Z</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -342,7 +342,7 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:26.385Z</t>
+    <t>2026-10-08T15:15:53.019Z</t>
   </si>
   <si>
     <t>WEB-026</t>
@@ -354,7 +354,7 @@
     <t>AI Studio</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:28.127Z</t>
+    <t>2026-10-08T15:15:53.924Z</t>
   </si>
   <si>
     <t>WEB-027</t>
@@ -363,7 +363,7 @@
     <t>Launch High-Yield Important Q&amp;A Generator</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:29.835Z</t>
+    <t>2026-10-08T15:15:54.769Z</t>
   </si>
   <si>
     <t>WEB-028</t>
@@ -372,7 +372,7 @@
     <t>Launch &amp; Configure Standalone MCQ Generator</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:31.634Z</t>
+    <t>2026-10-08T15:15:55.686Z</t>
   </si>
   <si>
     <t>WEB-029</t>
@@ -381,7 +381,7 @@
     <t>Execute Interactive Quiz Assessment</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:33.524Z</t>
+    <t>2026-10-08T15:15:57.412Z</t>
   </si>
   <si>
     <t>WEB-030</t>
@@ -390,7 +390,7 @@
     <t>Launch 24/7 AI Tutor Chat Assistant Interface</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:35.446Z</t>
+    <t>2026-10-08T15:15:59.170Z</t>
   </si>
   <si>
     <t>WEB-031</t>
@@ -402,7 +402,7 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:35.850Z</t>
+    <t>2026-10-08T15:15:59.389Z</t>
   </si>
   <si>
     <t>WEB-032</t>
@@ -414,7 +414,7 @@
     <t>PDF Viewer</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:36.312Z</t>
+    <t>2026-10-08T15:15:59.649Z</t>
   </si>
   <si>
     <t>WEB-033</t>
@@ -426,7 +426,7 @@
     <t>Search</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:36.608Z</t>
+    <t>2026-10-08T15:15:59.879Z</t>
   </si>
   <si>
     <t>WEB-034</t>
@@ -438,7 +438,7 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:37.337Z</t>
+    <t>2026-10-08T15:16:00.178Z</t>
   </si>
   <si>
     <t>WEB-035</t>
@@ -447,7 +447,7 @@
     <t>Profile Session Logout Execution</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:37.954Z</t>
+    <t>2026-10-08T15:16:00.485Z</t>
   </si>
   <si>
     <t>WEB-036</t>
@@ -459,7 +459,7 @@
     <t>Responsive</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:38.844Z</t>
+    <t>2026-10-08T15:16:01.221Z</t>
   </si>
   <si>
     <t>WEB-037</t>
@@ -471,7 +471,7 @@
     <t>Security</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:40.155Z</t>
+    <t>2026-10-08T15:16:02.077Z</t>
   </si>
   <si>
     <t>WEB-038</t>
@@ -480,7 +480,7 @@
     <t>Admin Route Security Access Protection</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:41.400Z</t>
+    <t>2026-10-08T15:16:03.261Z</t>
   </si>
   <si>
     <t>WEB-039</t>
@@ -489,7 +489,7 @@
     <t>Session Token Protection &amp; Authorization Guard</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:42.633Z</t>
+    <t>2026-10-08T15:16:04.425Z</t>
   </si>
   <si>
     <t>WEB-040</t>
@@ -498,7 +498,7 @@
     <t>Post-Logout Session Protection Check</t>
   </si>
   <si>
-    <t>2026-08-27T16:40:42.723Z</t>
+    <t>2026-10-08T15:16:04.498Z</t>
   </si>
   <si>
     <t>Feature</t>
@@ -1099,7 +1099,7 @@
         <v>27</v>
       </c>
       <c r="F2">
-        <v>1798</v>
+        <v>1836</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
@@ -1125,7 +1125,7 @@
         <v>27</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
         <v>28</v>
@@ -1151,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1177,7 +1177,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>21116</v>
+        <v>21151</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -1203,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="F6">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -1229,7 +1229,7 @@
         <v>27</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1255,7 +1255,7 @@
         <v>27</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -1307,7 +1307,7 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1333,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
         <v>28</v>
@@ -1359,7 +1359,7 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
@@ -1385,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>181</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
@@ -1411,7 +1411,7 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>922</v>
+        <v>882</v>
       </c>
       <c r="G14" t="s">
         <v>28</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>507</v>
+        <v>895</v>
       </c>
       <c r="G15" t="s">
         <v>28</v>
@@ -1463,7 +1463,7 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>526</v>
+        <v>170</v>
       </c>
       <c r="G16" t="s">
         <v>28</v>
@@ -1489,7 +1489,7 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>586</v>
+        <v>188</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
@@ -1515,7 +1515,7 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>954</v>
+        <v>179</v>
       </c>
       <c r="G18" t="s">
         <v>28</v>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>308</v>
+        <v>177</v>
       </c>
       <c r="G19" t="s">
         <v>28</v>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="G20" t="s">
         <v>28</v>
@@ -1593,7 +1593,7 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>1119</v>
+        <v>1072</v>
       </c>
       <c r="G21" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s">
         <v>28</v>
@@ -1671,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G24" t="s">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="G25" t="s">
         <v>28</v>
@@ -1723,7 +1723,7 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" t="s">
         <v>28</v>
@@ -1749,7 +1749,7 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>1493</v>
+        <v>694</v>
       </c>
       <c r="G27" t="s">
         <v>28</v>
@@ -1775,7 +1775,7 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>1474</v>
+        <v>659</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -1801,7 +1801,7 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>1477</v>
+        <v>726</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -1827,7 +1827,7 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>1614</v>
+        <v>1564</v>
       </c>
       <c r="G30" t="s">
         <v>28</v>
@@ -1853,7 +1853,7 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>1609</v>
+        <v>1572</v>
       </c>
       <c r="G31" t="s">
         <v>28</v>
@@ -1879,7 +1879,7 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="G32" t="s">
         <v>28</v>
@@ -1905,7 +1905,7 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="G33" t="s">
         <v>28</v>
@@ -1931,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G34" t="s">
         <v>28</v>
@@ -1957,7 +1957,7 @@
         <v>27</v>
       </c>
       <c r="F35">
-        <v>401</v>
+        <v>130</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -1983,7 +1983,7 @@
         <v>27</v>
       </c>
       <c r="F36">
-        <v>389</v>
+        <v>134</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2009,7 +2009,7 @@
         <v>27</v>
       </c>
       <c r="F37">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2035,7 +2035,7 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>875</v>
+        <v>671</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="F39">
-        <v>1157</v>
+        <v>1115</v>
       </c>
       <c r="G39" t="s">
         <v>28</v>
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="F40">
-        <v>1138</v>
+        <v>1084</v>
       </c>
       <c r="G40" t="s">
         <v>28</v>
@@ -2113,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G41" t="s">
         <v>28</v>
